--- a/basedatos_partidas/salida/descompuestos/CT-18-06-010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-18-06-010.xlsx
@@ -617,10 +617,10 @@
         <v>0.02</v>
       </c>
       <c r="G13" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="14">
@@ -643,10 +643,10 @@
         <v>1.6</v>
       </c>
       <c r="G14" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="H14" t="n">
-        <v>5.44</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="15">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>59.81</v>
+        <v>57.75</v>
       </c>
     </row>
     <row r="17">
@@ -854,10 +854,10 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>71.95</v>
+        <v>69.89</v>
       </c>
       <c r="H26" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="27">
@@ -873,7 +873,7 @@
       </c>
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="5" t="n">
-        <v>72.67</v>
+        <v>70.59</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-18-06-010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-18-06-010.xlsx
@@ -669,10 +669,10 @@
         <v>0.28</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="16">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>57.75</v>
+        <v>57.98</v>
       </c>
     </row>
     <row r="17">
@@ -854,7 +854,7 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>69.89</v>
+        <v>70.12</v>
       </c>
       <c r="H26" t="n">
         <v>0.7</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="5" t="n">
-        <v>70.59</v>
+        <v>70.81999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-18-06-010.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-18-06-010.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 18 Obras exteriores y urbanismo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Elementos exteriores complementarios</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
